--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run5/epoch_140/per_file_predictions_epoch_140.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run5/epoch_140/per_file_predictions_epoch_140.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="493">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="494">
   <si>
     <t>Filename</t>
   </si>
@@ -808,691 +808,694 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9960,0.0001,0.0018,0.0003</t>
-  </si>
-  <si>
-    <t>0.0015,0.0001,0.0002,0.9991</t>
-  </si>
-  <si>
-    <t>0.9952,0.0000,0.0004,0.0028</t>
-  </si>
-  <si>
-    <t>0.0899,0.0008,0.0002,0.9703</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0.9982,0.0000,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.0002,0.0037,0.9989</t>
+  </si>
+  <si>
+    <t>0.9994,0.0000,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.1388,0.0022,0.0020,0.9353</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9988,0.0003,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9999,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9981,0.0011,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.8070,0.0007,0.2108,0.0003</t>
+  </si>
+  <si>
+    <t>0.0454,0.0004,0.9715,0.0002</t>
+  </si>
+  <si>
+    <t>0.0363,0.0010,0.9852,0.0000</t>
+  </si>
+  <si>
+    <t>0.0060,0.0008,0.9920,0.0004</t>
+  </si>
+  <si>
+    <t>0.7877,0.0004,0.2585,0.0007</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9997,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0031,0.9942,0.0014,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9944,0.0001,0.0027,0.0000</t>
+  </si>
+  <si>
+    <t>0.1995,0.0005,0.8458,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.1641,0.0004,0.8762,0.0001</t>
+  </si>
+  <si>
+    <t>0.0203,0.0002,0.9903,0.0000</t>
+  </si>
+  <si>
+    <t>0.0028,0.0003,0.9979,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.9999,0.0002</t>
+  </si>
+  <si>
+    <t>0.2914,0.7107,0.0030,0.0004</t>
+  </si>
+  <si>
+    <t>0.7090,0.0066,0.2036,0.0015</t>
+  </si>
+  <si>
+    <t>0.0000,0.0032,0.9999,0.0009</t>
+  </si>
+  <si>
+    <t>0.0108,0.9875,0.0021,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9986,0.0003,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.3785,0.7637,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.9977,0.0047,0.0001</t>
+  </si>
+  <si>
+    <t>0.0013,0.0480,0.9838,0.0007</t>
+  </si>
+  <si>
+    <t>0.0034,0.0042,0.9899,0.0022</t>
+  </si>
+  <si>
+    <t>0.0009,0.0019,0.9975,0.0003</t>
+  </si>
+  <si>
+    <t>0.0097,0.0001,0.9920,0.0003</t>
+  </si>
+  <si>
+    <t>0.0009,0.0011,0.9990,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9988,0.0033,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0006,0.9997,0.0001</t>
+  </si>
+  <si>
+    <t>0.0015,0.0204,0.0003,0.9969</t>
+  </si>
+  <si>
+    <t>0.0000,0.9997,0.0012,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.9989,0.0012,0.0005</t>
+  </si>
+  <si>
+    <t>0.0001,0.9994,0.0035,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.0053,0.9996,0.0002</t>
+  </si>
+  <si>
+    <t>0.0040,0.0358,0.9860,0.0001</t>
+  </si>
+  <si>
+    <t>0.0208,0.0007,0.9850,0.0002</t>
+  </si>
+  <si>
+    <t>0.0003,0.0002,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0003,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0013,0.0020,0.9978,0.0000</t>
+  </si>
+  <si>
+    <t>0.9896,0.0085,0.0013,0.0002</t>
+  </si>
+  <si>
+    <t>0.9988,0.0000,0.0008,0.0002</t>
+  </si>
+  <si>
+    <t>0.9993,0.0001,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0055,0.9999,0.0006</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9984,0.0011,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9973,0.0011,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9989,0.9711,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0004,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,0.9999,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9880,0.9982,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0005,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.9993,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0008,0.9993,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.6396,0.0038,0.4262,0.0001</t>
+  </si>
+  <si>
+    <t>0.9944,0.0005,0.0023,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0017,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9694,0.9881,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9938,0.1982,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9994,0.9441,0.0000</t>
+  </si>
+  <si>
+    <t>0.0023,0.0001,0.0022,0.9973</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0002,0.9999</t>
+  </si>
+  <si>
+    <t>0.0009,0.0001,0.0000,0.9997</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0005,0.9956,0.0065,0.0004</t>
+  </si>
+  <si>
+    <t>0.0000,0.9978,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9544,0.9941,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9723,0.9681,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9979,0.9979,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9872,0.8113,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9988,0.0003,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9990,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>1.0000,0.0000,0.0000,0.0000</t>
   </si>
   <si>
     <t>0.9998,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9932,0.0046,0.0006,0.0002</t>
-  </si>
-  <si>
-    <t>0.9977,0.0004,0.0008,0.0003</t>
+    <t>0.0007,0.0002,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.0006,0.0022,0.9993,0.0000</t>
+  </si>
+  <si>
+    <t>0.9836,0.0010,0.0065,0.0003</t>
+  </si>
+  <si>
+    <t>0.0009,0.0006,0.9990,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9996,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9994,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9997,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9649,0.0494,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9573,0.0014,0.0296,0.0004</t>
+  </si>
+  <si>
+    <t>0.9942,0.0003,0.0021,0.0000</t>
+  </si>
+  <si>
+    <t>0.9793,0.0015,0.0093,0.0002</t>
+  </si>
+  <si>
+    <t>0.9380,0.0009,0.0502,0.0008</t>
+  </si>
+  <si>
+    <t>0.0005,0.0127,0.0078,0.9784</t>
+  </si>
+  <si>
+    <t>0.0000,0.9997,0.0096,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9995,0.0009,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9946,0.9986,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9996,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.8566,0.1599,0.0021,0.0001</t>
+  </si>
+  <si>
+    <t>0.1761,0.8336,0.0021,0.0004</t>
+  </si>
+  <si>
+    <t>0.9963,0.0004,0.0020,0.0003</t>
+  </si>
+  <si>
+    <t>0.9995,0.0000,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9990,0.0000,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.9978,0.0005,0.0007,0.0002</t>
+  </si>
+  <si>
+    <t>0.9995,0.0000,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9992,0.0001,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.0004,0.0717,0.9933,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.0695,0.9993,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0041,0.9994,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0035,0.9995,0.0000</t>
+  </si>
+  <si>
+    <t>0.9974,0.0000,0.0014,0.0000</t>
+  </si>
+  <si>
+    <t>0.0144,0.0039,0.9818,0.0006</t>
+  </si>
+  <si>
+    <t>0.8962,0.0002,0.1536,0.0001</t>
+  </si>
+  <si>
+    <t>0.9648,0.0021,0.0187,0.0013</t>
+  </si>
+  <si>
+    <t>0.0071,0.0000,0.0001,0.9983</t>
+  </si>
+  <si>
+    <t>0.0000,0.0008,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0000,0.9975,0.6171,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0049,0.9914,0.0009,0.0006</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.0312,0.9590,0.0085,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0000,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.0034,0.0001,0.0021,0.9977</t>
+  </si>
+  <si>
+    <t>0.0008,0.0062,0.9979,0.0012</t>
+  </si>
+  <si>
+    <t>0.9801,0.0000,0.0011,0.0232</t>
+  </si>
+  <si>
+    <t>0.9987,0.0000,0.0001,0.0016</t>
+  </si>
+  <si>
+    <t>0.0422,0.9077,0.0286,0.0014</t>
+  </si>
+  <si>
+    <t>0.9951,0.0007,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.9982,0.0001,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0324,0.8325,0.0273,0.0029</t>
+  </si>
+  <si>
+    <t>0.9768,0.0049,0.0055,0.0003</t>
+  </si>
+  <si>
+    <t>0.9824,0.0082,0.0033,0.0001</t>
+  </si>
+  <si>
+    <t>0.9980,0.0002,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.9985,0.0002,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.9999,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9992,0.0002,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9870,0.0085,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.8988,0.0890,0.0052,0.0002</t>
+  </si>
+  <si>
+    <t>0.4258,0.6140,0.0024,0.0002</t>
+  </si>
+  <si>
+    <t>0.0123,0.0056,0.9822,0.0011</t>
+  </si>
+  <si>
+    <t>0.9979,0.0012,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9975,0.0004,0.0005,0.0005</t>
+  </si>
+  <si>
+    <t>0.9872,0.0015,0.0037,0.0009</t>
+  </si>
+  <si>
+    <t>0.0000,0.0006,1.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9156,0.0213,0.0079,0.0047</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.0019,0.9985,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0691,0.0132,0.8978,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.0044,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0634,0.0005,0.9470,0.0005</t>
+  </si>
+  <si>
+    <t>0.0052,0.0008,0.9952,0.0001</t>
+  </si>
+  <si>
+    <t>0.0048,0.0025,0.9921,0.0004</t>
+  </si>
+  <si>
+    <t>0.8284,0.0102,0.0984,0.0003</t>
+  </si>
+  <si>
+    <t>0.1659,0.6903,0.0265,0.0001</t>
+  </si>
+  <si>
+    <t>0.9430,0.0097,0.0249,0.0003</t>
+  </si>
+  <si>
+    <t>0.9634,0.0036,0.0107,0.0013</t>
+  </si>
+  <si>
+    <t>0.0324,0.0049,0.9583,0.0008</t>
+  </si>
+  <si>
+    <t>0.9760,0.0321,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0014,0.9967,0.0027,0.0000</t>
+  </si>
+  <si>
+    <t>0.9171,0.1254,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.9933,0.0096,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.3036,0.8323,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9979,0.0006,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9986,0.0000,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.9402,0.0034,0.0272,0.0023</t>
+  </si>
+  <si>
+    <t>0.8284,0.0067,0.0752,0.0030</t>
+  </si>
+  <si>
+    <t>0.0459,0.0073,0.9552,0.0005</t>
+  </si>
+  <si>
+    <t>0.0004,0.0027,0.9988,0.0001</t>
+  </si>
+  <si>
+    <t>0.0031,0.0024,0.9959,0.0001</t>
+  </si>
+  <si>
+    <t>0.0009,0.0007,0.9986,0.0000</t>
+  </si>
+  <si>
+    <t>0.0031,0.0064,0.9911,0.0003</t>
+  </si>
+  <si>
+    <t>0.9981,0.0002,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9969,0.0007,0.0010,0.0001</t>
+  </si>
+  <si>
+    <t>0.9979,0.0010,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9990,0.0006,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9944,0.0016,0.0009,0.0008</t>
+  </si>
+  <si>
+    <t>0.9995,0.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0041,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.0148,0.4422,0.4004,0.0005</t>
+  </si>
+  <si>
+    <t>0.9888,0.0004,0.0056,0.0012</t>
+  </si>
+  <si>
+    <t>0.0110,0.0002,0.9953,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0028,0.9992,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.0803,0.9991,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0001,0.9995,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0006,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0011,0.9983,0.0009</t>
+  </si>
+  <si>
+    <t>0.0004,0.0010,0.9988,0.0002</t>
+  </si>
+  <si>
+    <t>0.6684,0.0002,0.4693,0.0004</t>
+  </si>
+  <si>
+    <t>0.9194,0.0002,0.1252,0.0003</t>
+  </si>
+  <si>
+    <t>0.2862,0.0006,0.8108,0.0007</t>
+  </si>
+  <si>
+    <t>0.9985,0.0010,0.0001,0.0000</t>
   </si>
   <si>
     <t>0.9991,0.0002,0.0002,0.0001</t>
   </si>
   <si>
-    <t>0.9997,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0002,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.3084,0.0013,0.7431,0.0003</t>
-  </si>
-  <si>
-    <t>0.0243,0.0003,0.9827,0.0002</t>
-  </si>
-  <si>
-    <t>0.9414,0.0007,0.0710,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.0012,0.9980,0.0002</t>
-  </si>
-  <si>
-    <t>0.9388,0.0008,0.0466,0.0006</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0014,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9997,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0026,0.9955,0.0010,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9879,0.0002,0.0064,0.0001</t>
-  </si>
-  <si>
-    <t>0.1986,0.0004,0.8532,0.0004</t>
-  </si>
-  <si>
-    <t>0.0003,0.0001,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0020,0.0004,0.9978,0.0000</t>
-  </si>
-  <si>
-    <t>0.3691,0.0001,0.8138,0.0000</t>
-  </si>
-  <si>
-    <t>0.0028,0.0001,0.9981,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9999,0.0002</t>
-  </si>
-  <si>
-    <t>0.2224,0.8413,0.0008,0.0003</t>
-  </si>
-  <si>
-    <t>0.6764,0.0031,0.2513,0.0018</t>
-  </si>
-  <si>
-    <t>0.0002,0.0019,0.9996,0.0009</t>
-  </si>
-  <si>
-    <t>0.0033,0.9955,0.0011,0.0000</t>
-  </si>
-  <si>
-    <t>0.9990,0.0003,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.1254,0.0227,0.8187,0.0044</t>
-  </si>
-  <si>
-    <t>0.7908,0.3059,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9996,0.0019,0.0001</t>
-  </si>
-  <si>
-    <t>0.0013,0.4889,0.7503,0.0017</t>
-  </si>
-  <si>
-    <t>0.0076,0.0018,0.9846,0.0038</t>
-  </si>
-  <si>
-    <t>0.0005,0.0038,0.9982,0.0002</t>
-  </si>
-  <si>
-    <t>0.0008,0.0003,0.9985,0.0006</t>
-  </si>
-  <si>
-    <t>0.0005,0.0267,0.9990,0.0000</t>
-  </si>
-  <si>
-    <t>0.0010,0.9866,0.0200,0.0004</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0085,0.0256,0.0002,0.9914</t>
-  </si>
-  <si>
-    <t>0.0001,0.9994,0.0009,0.0005</t>
-  </si>
-  <si>
-    <t>0.0002,0.9989,0.0015,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0014,0.9998,0.0002</t>
-  </si>
-  <si>
-    <t>0.0011,0.0008,0.9987,0.0000</t>
-  </si>
-  <si>
-    <t>0.0633,0.0004,0.9509,0.0002</t>
-  </si>
-  <si>
-    <t>0.0003,0.0001,0.9997,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0012,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0006,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9952,0.0020,0.0010,0.0002</t>
-  </si>
-  <si>
-    <t>0.9982,0.0001,0.0007,0.0008</t>
-  </si>
-  <si>
-    <t>0.9926,0.0008,0.0051,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.0013,0.9998,0.0017</t>
-  </si>
-  <si>
-    <t>0.9989,0.0003,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9978,0.0017,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9984,0.0005,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9967,0.9960,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0017,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0004,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9932,0.9955,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9996,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0058,0.9977,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9981,0.0001,0.0008,0.0000</t>
-  </si>
-  <si>
-    <t>0.7474,0.0112,0.2066,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0010,1.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9842,0.9946,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9993,0.9729,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0079,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0032,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.0038,0.9992</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0000,0.0001,0.9998</t>
-  </si>
-  <si>
-    <t>0.0015,0.0001,0.0000,0.9996</t>
-  </si>
-  <si>
-    <t>0.0000,0.9967,0.2502,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9833,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9741,0.8203,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9918,0.9673,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9965,0.9883,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9843,0.6158,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9982,0.0006,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9984,0.0002,0.0006,0.0002</t>
-  </si>
-  <si>
-    <t>0.9972,0.0006,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0003,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9985,0.0005,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9991,0.0003,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9999,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>1.0000,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9999,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0499,0.0033,0.9564,0.0000</t>
-  </si>
-  <si>
-    <t>0.9797,0.0004,0.0164,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9995,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.9992,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.9991,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0006,0.9994,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9643,0.0556,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.8616,0.0006,0.1104,0.0013</t>
-  </si>
-  <si>
-    <t>0.9942,0.0003,0.0019,0.0000</t>
-  </si>
-  <si>
-    <t>0.8820,0.0082,0.0492,0.0008</t>
-  </si>
-  <si>
-    <t>0.7934,0.0007,0.1743,0.0022</t>
-  </si>
-  <si>
-    <t>0.0011,0.0075,0.0008,0.9958</t>
-  </si>
-  <si>
-    <t>0.0001,0.9991,0.0658,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.0001,0.0006</t>
-  </si>
-  <si>
-    <t>0.0000,0.9691,0.9898,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9995,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.4089,0.6099,0.0059,0.0001</t>
-  </si>
-  <si>
-    <t>0.7786,0.2613,0.0010,0.0002</t>
-  </si>
-  <si>
-    <t>0.9980,0.0003,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0000,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0000,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9981,0.0002,0.0010,0.0002</t>
-  </si>
-  <si>
-    <t>0.9988,0.0001,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0006,0.0234,0.9900,0.0010</t>
-  </si>
-  <si>
-    <t>0.0001,0.1089,0.9984,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.9949,0.0001,0.0019,0.0001</t>
-  </si>
-  <si>
-    <t>0.3529,0.0026,0.6604,0.0011</t>
-  </si>
-  <si>
-    <t>0.9945,0.0001,0.0037,0.0000</t>
-  </si>
-  <si>
-    <t>0.9891,0.0006,0.0052,0.0001</t>
-  </si>
-  <si>
-    <t>0.0138,0.0000,0.0006,0.9951</t>
-  </si>
-  <si>
-    <t>0.0000,0.0004,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9920,0.9144,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0000,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.0615,0.9375,0.0009,0.0004</t>
-  </si>
-  <si>
-    <t>0.7730,0.1682,0.0070,0.0001</t>
-  </si>
-  <si>
-    <t>0.9988,0.0000,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.0204,0.0001,0.0004,0.9940</t>
-  </si>
-  <si>
-    <t>0.0044,0.0149,0.9848,0.0045</t>
-  </si>
-  <si>
-    <t>0.9812,0.0000,0.0010,0.0162</t>
-  </si>
-  <si>
-    <t>0.9994,0.0000,0.0001,0.0007</t>
-  </si>
-  <si>
-    <t>0.0092,0.9785,0.0066,0.0012</t>
-  </si>
-  <si>
-    <t>0.9947,0.0007,0.0008,0.0002</t>
-  </si>
-  <si>
-    <t>0.9977,0.0002,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.8772,0.0574,0.0068,0.0014</t>
-  </si>
-  <si>
-    <t>0.9749,0.0056,0.0061,0.0003</t>
-  </si>
-  <si>
-    <t>0.9524,0.0546,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0000,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9984,0.0002,0.0006,0.0004</t>
-  </si>
-  <si>
-    <t>0.9993,0.0001,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9992,0.0001,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9989,0.0001,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.9995,0.0000,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9957,0.0011,0.0000,0.0005</t>
-  </si>
-  <si>
-    <t>0.9391,0.0440,0.0070,0.0001</t>
-  </si>
-  <si>
-    <t>0.9395,0.0514,0.0031,0.0002</t>
-  </si>
-  <si>
-    <t>0.0498,0.0136,0.9453,0.0006</t>
-  </si>
-  <si>
-    <t>0.9568,0.0536,0.0015,0.0001</t>
-  </si>
-  <si>
-    <t>0.9958,0.0005,0.0006,0.0008</t>
-  </si>
-  <si>
-    <t>0.9993,0.0002,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9793,0.0061,0.0057,0.0004</t>
-  </si>
-  <si>
-    <t>0.0000,0.0013,1.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9525,0.0137,0.0076,0.0028</t>
-  </si>
-  <si>
-    <t>0.0037,0.0066,0.9871,0.0015</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0037,0.0175,0.9867,0.0009</t>
-  </si>
-  <si>
-    <t>0.0000,0.0015,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0138,0.0005,0.9872,0.0002</t>
-  </si>
-  <si>
-    <t>0.0022,0.0001,0.9989,0.0000</t>
-  </si>
-  <si>
-    <t>0.0098,0.0024,0.9872,0.0005</t>
-  </si>
-  <si>
-    <t>0.0835,0.0076,0.8752,0.0008</t>
-  </si>
-  <si>
-    <t>0.0085,0.9708,0.0214,0.0002</t>
-  </si>
-  <si>
-    <t>0.9906,0.0012,0.0025,0.0000</t>
-  </si>
-  <si>
-    <t>0.9822,0.0010,0.0074,0.0002</t>
-  </si>
-  <si>
-    <t>0.0069,0.0236,0.9803,0.0004</t>
-  </si>
-  <si>
-    <t>0.9894,0.0109,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0456,0.9556,0.0058,0.0000</t>
-  </si>
-  <si>
-    <t>0.9590,0.0583,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9979,0.0030,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9651,0.0592,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9748,0.0143,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9988,0.0001,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9912,0.0003,0.0023,0.0006</t>
-  </si>
-  <si>
-    <t>0.9377,0.0012,0.0481,0.0006</t>
-  </si>
-  <si>
-    <t>0.9868,0.0010,0.0047,0.0004</t>
-  </si>
-  <si>
-    <t>0.0197,0.0010,0.9847,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.0052,0.9995,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0030,0.9993,0.0000</t>
-  </si>
-  <si>
-    <t>0.0326,0.0024,0.9584,0.0004</t>
-  </si>
-  <si>
-    <t>0.0006,0.0019,0.9979,0.0002</t>
-  </si>
-  <si>
-    <t>0.9952,0.0011,0.0011,0.0005</t>
-  </si>
-  <si>
-    <t>0.9974,0.0005,0.0011,0.0002</t>
-  </si>
-  <si>
-    <t>0.9986,0.0008,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9965,0.0013,0.0005,0.0003</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0046,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0281,0.1057,0.8701,0.0004</t>
-  </si>
-  <si>
-    <t>0.9690,0.0005,0.0229,0.0018</t>
-  </si>
-  <si>
-    <t>0.0082,0.0011,0.9963,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0076,0.9997,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0555,0.9994,0.0000</t>
-  </si>
-  <si>
-    <t>0.0011,0.0004,0.9983,0.0001</t>
-  </si>
-  <si>
-    <t>0.0007,0.0005,0.9984,0.0001</t>
-  </si>
-  <si>
-    <t>0.0013,0.0005,0.9982,0.0002</t>
-  </si>
-  <si>
-    <t>0.9537,0.0000,0.0891,0.0001</t>
-  </si>
-  <si>
-    <t>0.2939,0.0001,0.8272,0.0003</t>
-  </si>
-  <si>
-    <t>0.9908,0.0002,0.0068,0.0001</t>
-  </si>
-  <si>
-    <t>0.9959,0.0030,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9988,0.0002,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9990,0.0001,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9966,0.0024,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0008,0.0020,0.9976,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0006,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0070,0.9983,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.0775,0.9924,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.0962,0.0002,0.9220,0.0008</t>
-  </si>
-  <si>
-    <t>0.2675,0.0013,0.6541,0.0016</t>
-  </si>
-  <si>
-    <t>0.0003,0.0000,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.9714,0.0001,0.0015,0.0226</t>
-  </si>
-  <si>
-    <t>0.0002,0.0057,0.0001,0.9994</t>
-  </si>
-  <si>
-    <t>0.2032,0.0000,0.0001,0.9565</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.1780,0.0094,0.0009,0.8936</t>
+    <t>0.9977,0.0015,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9991,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9800,0.0307,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0041,0.9984,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0018,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0035,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.0044,0.9985,0.0000</t>
+  </si>
+  <si>
+    <t>0.0028,0.0002,0.9982,0.0001</t>
+  </si>
+  <si>
+    <t>0.0064,0.0009,0.9923,0.0005</t>
+  </si>
+  <si>
+    <t>0.0529,0.0072,0.8754,0.0033</t>
+  </si>
+  <si>
+    <t>0.0011,0.0004,0.9984,0.0002</t>
+  </si>
+  <si>
+    <t>0.7163,0.0000,0.0580,0.0812</t>
+  </si>
+  <si>
+    <t>0.0003,0.0683,0.0001,0.9982</t>
+  </si>
+  <si>
+    <t>0.0033,0.0000,0.0002,0.9989</t>
+  </si>
+  <si>
+    <t>0.9649,0.0008,0.0005,0.0196</t>
   </si>
 </sst>
 </file>
@@ -1878,7 +1881,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1892,7 +1895,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1906,7 +1909,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1920,7 +1923,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1934,7 +1937,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1948,7 +1951,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1962,7 +1965,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1976,7 +1979,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1990,7 +1993,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2004,7 +2007,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2018,7 +2021,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2032,7 +2035,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2043,10 +2046,10 @@
         <v>259</v>
       </c>
       <c r="C14" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2060,7 +2063,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2071,10 +2074,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2088,7 +2091,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2102,7 +2105,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2116,7 +2119,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2130,7 +2133,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2144,7 +2147,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2158,7 +2161,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2172,7 +2175,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2186,7 +2189,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2200,7 +2203,7 @@
         <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2214,7 +2217,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2228,7 +2231,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2242,7 +2245,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2256,7 +2259,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2270,7 +2273,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2284,7 +2287,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2298,7 +2301,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2312,7 +2315,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2326,7 +2329,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2340,7 +2343,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2351,10 +2354,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2365,10 +2368,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2382,7 +2385,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2396,7 +2399,7 @@
         <v>261</v>
       </c>
       <c r="D39" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2410,7 +2413,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2424,7 +2427,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2438,7 +2441,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2452,7 +2455,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2466,7 +2469,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2480,7 +2483,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2494,7 +2497,7 @@
         <v>260</v>
       </c>
       <c r="D46" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2508,7 +2511,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2522,7 +2525,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2536,7 +2539,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2550,7 +2553,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2564,7 +2567,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2578,7 +2581,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2592,7 +2595,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2606,7 +2609,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2620,7 +2623,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2634,7 +2637,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2648,7 +2651,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2662,7 +2665,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2676,7 +2679,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2690,7 +2693,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2704,7 +2707,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2718,7 +2721,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2732,7 +2735,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2746,7 +2749,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2760,7 +2763,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2774,7 +2777,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2788,7 +2791,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>306</v>
+        <v>329</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2802,7 +2805,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2816,7 +2819,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2830,7 +2833,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2844,7 +2847,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2858,7 +2861,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2872,7 +2875,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2883,10 +2886,10 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D74" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2900,7 +2903,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2911,10 +2914,10 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2928,7 +2931,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2942,7 +2945,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2956,7 +2959,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2970,7 +2973,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2984,7 +2987,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2998,7 +3001,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3012,7 +3015,7 @@
         <v>262</v>
       </c>
       <c r="D83" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3026,7 +3029,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3040,7 +3043,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3054,7 +3057,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3068,7 +3071,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3082,7 +3085,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3096,7 +3099,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3110,7 +3113,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>349</v>
+        <v>273</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3124,7 +3127,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3138,7 +3141,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3152,7 +3155,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>352</v>
+        <v>275</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3166,7 +3169,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>353</v>
+        <v>275</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3180,7 +3183,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3194,7 +3197,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>355</v>
+        <v>269</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3208,7 +3211,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3222,7 +3225,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3236,7 +3239,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3250,7 +3253,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>356</v>
+        <v>272</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3264,7 +3267,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3278,7 +3281,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>359</v>
+        <v>272</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3292,7 +3295,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>360</v>
+        <v>272</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3306,7 +3309,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3320,7 +3323,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3334,7 +3337,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3348,7 +3351,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3362,7 +3365,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3376,7 +3379,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3390,7 +3393,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3404,7 +3407,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3418,7 +3421,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3432,7 +3435,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3446,7 +3449,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3460,7 +3463,7 @@
         <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3474,7 +3477,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3488,7 +3491,7 @@
         <v>259</v>
       </c>
       <c r="D117" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3502,7 +3505,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3516,7 +3519,7 @@
         <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3530,7 +3533,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3544,7 +3547,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3558,7 +3561,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3572,7 +3575,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>284</v>
+        <v>373</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3586,7 +3589,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3600,7 +3603,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3611,10 +3614,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3625,10 +3628,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D127" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3642,7 +3645,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3656,7 +3659,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3670,7 +3673,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3684,7 +3687,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3698,7 +3701,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>383</v>
+        <v>355</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3712,7 +3715,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3726,7 +3729,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3740,7 +3743,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3754,7 +3757,7 @@
         <v>261</v>
       </c>
       <c r="D136" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3768,7 +3771,7 @@
         <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3782,7 +3785,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>316</v>
+        <v>387</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3796,7 +3799,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3810,7 +3813,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3824,7 +3827,7 @@
         <v>261</v>
       </c>
       <c r="D141" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3838,7 +3841,7 @@
         <v>259</v>
       </c>
       <c r="D142" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3852,7 +3855,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3866,7 +3869,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3880,7 +3883,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3894,7 +3897,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3908,7 +3911,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>339</v>
+        <v>395</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3922,7 +3925,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3936,7 +3939,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3950,7 +3953,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3964,7 +3967,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>384</v>
+        <v>399</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3975,10 +3978,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3992,7 +3995,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4006,7 +4009,7 @@
         <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4020,7 +4023,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>356</v>
+        <v>397</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4034,7 +4037,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4048,7 +4051,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4062,7 +4065,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4076,7 +4079,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4090,7 +4093,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4104,7 +4107,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4115,10 +4118,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4132,7 +4135,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4146,7 +4149,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4160,7 +4163,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4174,7 +4177,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>383</v>
+        <v>355</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4188,7 +4191,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4202,7 +4205,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4216,7 +4219,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4230,7 +4233,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>350</v>
+        <v>415</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4244,7 +4247,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4258,7 +4261,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4272,7 +4275,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4286,7 +4289,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4297,10 +4300,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4314,7 +4317,7 @@
         <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4328,7 +4331,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4342,7 +4345,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4356,7 +4359,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>425</v>
+        <v>322</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4370,7 +4373,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4384,7 +4387,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4398,7 +4401,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4412,7 +4415,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>306</v>
+        <v>427</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4426,7 +4429,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4440,7 +4443,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4454,7 +4457,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4468,7 +4471,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4482,7 +4485,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>361</v>
+        <v>432</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4496,7 +4499,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>361</v>
+        <v>432</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4549,7 +4552,7 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D193" t="s">
         <v>436</v>
@@ -4675,7 +4678,7 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D202" t="s">
         <v>445</v>
@@ -4745,7 +4748,7 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D207" t="s">
         <v>450</v>
@@ -4762,7 +4765,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>451</v>
+        <v>315</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4776,7 +4779,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4790,7 +4793,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4804,7 +4807,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4818,7 +4821,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4832,7 +4835,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4846,7 +4849,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4860,7 +4863,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4874,7 +4877,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4888,7 +4891,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>415</v>
+        <v>459</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4902,7 +4905,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4916,7 +4919,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4930,7 +4933,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4944,7 +4947,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4955,10 +4958,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D222" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4972,7 +4975,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4986,7 +4989,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5000,7 +5003,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5014,7 +5017,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5028,7 +5031,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>306</v>
+        <v>429</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5042,7 +5045,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5056,7 +5059,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>306</v>
+        <v>470</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5070,7 +5073,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5084,7 +5087,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5098,7 +5101,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5109,10 +5112,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5123,10 +5126,10 @@
         <v>259</v>
       </c>
       <c r="C234" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D234" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5140,7 +5143,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5154,7 +5157,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5168,7 +5171,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5182,7 +5185,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5196,7 +5199,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5210,7 +5213,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>478</v>
+        <v>269</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5224,7 +5227,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5238,7 +5241,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>360</v>
+        <v>481</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5252,7 +5255,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5266,7 +5269,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5280,7 +5283,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5294,7 +5297,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5308,7 +5311,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5322,7 +5325,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5336,7 +5339,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5350,7 +5353,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5364,7 +5367,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5378,7 +5381,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5392,7 +5395,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5406,7 +5409,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>491</v>
+        <v>340</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5420,7 +5423,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5431,10 +5434,10 @@
         <v>259</v>
       </c>
       <c r="C256" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
   </sheetData>
